--- a/data/trans_dic/P25C_R2_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25C_R2_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos)</t>
+          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,19</t>
+          <t>1,7; 6,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,87</t>
+          <t>0,0; 6,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,45</t>
+          <t>1,74; 5,45</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,73</t>
+          <t>0,19; 2,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,83</t>
+          <t>2,5; 6,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,56</t>
+          <t>0,72; 3,52</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,97</t>
+          <t>0,41; 3,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 9,51</t>
+          <t>1,65; 9,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,9</t>
+          <t>1,23; 5,1</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,8</t>
+          <t>0,65; 2,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,8</t>
+          <t>2,49; 6,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,36</t>
+          <t>1,06; 3,28</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos)</t>
+          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2887; 10257</t>
+          <t>2810; 10360</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3044</t>
+          <t>0; 3080</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3339; 11452</t>
+          <t>3665; 11447</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>605; 14872</t>
+          <t>1019; 14852</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4999; 13882</t>
+          <t>5087; 14041</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5743; 26643</t>
+          <t>5401; 26333</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>587; 5446</t>
+          <t>566; 5414</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1291; 8280</t>
+          <t>1435; 8603</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2693; 10999</t>
+          <t>2767; 11443</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4896; 23743</t>
+          <t>5518; 23694</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8358; 19413</t>
+          <t>8321; 20084</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13531; 39745</t>
+          <t>12497; 38824</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C_R2_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25C_R2_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,25</t>
+          <t>1,87; 6,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,95</t>
+          <t>0,0; 7,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,45</t>
+          <t>1,62; 5,51</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,73</t>
+          <t>0,78; 3,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,91</t>
+          <t>2,5; 6,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,52</t>
+          <t>1,78; 4,48</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,94</t>
+          <t>0,39; 3,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 9,88</t>
+          <t>1,59; 10,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,1</t>
+          <t>1,35; 4,86</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,8</t>
+          <t>1,35; 3,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,0</t>
+          <t>2,64; 6,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,28</t>
+          <t>2,12; 3,96</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>609</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>7188</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2810; 10360</t>
+          <t>3285; 12026</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3080</t>
+          <t>0; 3531</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3665; 11447</t>
+          <t>3622; 12299</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>9398</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15786</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1019; 14852</t>
+          <t>2585; 12401</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5087; 14041</t>
+          <t>5561; 14966</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5401; 26333</t>
+          <t>9867; 24872</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>6487</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>566; 5414</t>
+          <t>585; 5169</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1435; 8603</t>
+          <t>1517; 9828</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2767; 11443</t>
+          <t>3289; 11866</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>29461</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5518; 23694</t>
+          <t>8896; 22125</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8321; 20084</t>
+          <t>9639; 21906</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12497; 38824</t>
+          <t>21707; 40435</t>
         </is>
       </c>
     </row>
